--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43572,7 +43572,7 @@
     </row>
     <row r="1608">
       <c r="A1608" s="1" t="n">
-        <v>45940.6384143519</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B1608" t="n">
         <v>64000</v>
@@ -43593,6 +43593,32 @@
         <v>305</v>
       </c>
       <c r="H1608" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="1" t="n">
+        <v>45943.6494444444</v>
+      </c>
+      <c r="B1609" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1609" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="D1609" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E1609" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="F1609" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G1609" t="s">
+        <v>305</v>
+      </c>
+      <c r="H1609" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43598,7 +43598,7 @@
     </row>
     <row r="1609">
       <c r="A1609" s="1" t="n">
-        <v>45943.6494444444</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B1609" t="n">
         <v>3000</v>
@@ -43619,6 +43619,32 @@
         <v>305</v>
       </c>
       <c r="H1609" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="1" t="n">
+        <v>45944.3674884259</v>
+      </c>
+      <c r="B1610" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1610" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D1610" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E1610" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F1610" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G1610" t="s">
+        <v>305</v>
+      </c>
+      <c r="H1610" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43624,7 +43624,7 @@
     </row>
     <row r="1610">
       <c r="A1610" s="1" t="n">
-        <v>45944.3674884259</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B1610" t="n">
         <v>9000</v>
@@ -43645,6 +43645,32 @@
         <v>305</v>
       </c>
       <c r="H1610" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="1" t="n">
+        <v>45945.6440856481</v>
+      </c>
+      <c r="B1611" t="n">
+        <v>194000</v>
+      </c>
+      <c r="C1611" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="D1611" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E1611" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F1611" t="n">
+        <v>2.28999996185303</v>
+      </c>
+      <c r="G1611" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1611" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43650,7 +43650,7 @@
     </row>
     <row r="1611">
       <c r="A1611" s="1" t="n">
-        <v>45945.6440856481</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B1611" t="n">
         <v>194000</v>
@@ -43671,6 +43671,32 @@
         <v>132</v>
       </c>
       <c r="H1611" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="1" t="n">
+        <v>45946.6451157407</v>
+      </c>
+      <c r="B1612" t="n">
+        <v>58000</v>
+      </c>
+      <c r="C1612" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="D1612" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="E1612" t="n">
+        <v>2.28999996185303</v>
+      </c>
+      <c r="F1612" t="n">
+        <v>2.28999996185303</v>
+      </c>
+      <c r="G1612" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1612" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43676,7 +43676,7 @@
     </row>
     <row r="1612">
       <c r="A1612" s="1" t="n">
-        <v>45946.6451157407</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B1612" t="n">
         <v>58000</v>
@@ -43697,6 +43697,32 @@
         <v>132</v>
       </c>
       <c r="H1612" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="1" t="n">
+        <v>45947.6493981481</v>
+      </c>
+      <c r="B1613" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C1613" t="n">
+        <v>2.28999996185303</v>
+      </c>
+      <c r="D1613" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E1613" t="n">
+        <v>2.28999996185303</v>
+      </c>
+      <c r="F1613" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G1613" t="s">
+        <v>305</v>
+      </c>
+      <c r="H1613" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43702,7 +43702,7 @@
     </row>
     <row r="1613">
       <c r="A1613" s="1" t="n">
-        <v>45947.6493981481</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B1613" t="n">
         <v>24000</v>
@@ -43711,7 +43711,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="D1613" t="n">
-        <v>2.25999999046326</v>
+        <v>2.25</v>
       </c>
       <c r="E1613" t="n">
         <v>2.28999996185303</v>
@@ -43723,6 +43723,32 @@
         <v>305</v>
       </c>
       <c r="H1613" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="1" t="n">
+        <v>45950.5718055556</v>
+      </c>
+      <c r="B1614" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C1614" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D1614" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E1614" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F1614" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G1614" t="s">
+        <v>305</v>
+      </c>
+      <c r="H1614" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43728,7 +43728,7 @@
     </row>
     <row r="1614">
       <c r="A1614" s="1" t="n">
-        <v>45950.5718055556</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B1614" t="n">
         <v>15000</v>
@@ -43749,6 +43749,32 @@
         <v>305</v>
       </c>
       <c r="H1614" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="1" t="n">
+        <v>45951.6496180556</v>
+      </c>
+      <c r="B1615" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C1615" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="D1615" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E1615" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="F1615" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G1615" t="s">
+        <v>320</v>
+      </c>
+      <c r="H1615" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43754,13 +43754,13 @@
     </row>
     <row r="1615">
       <c r="A1615" s="1" t="n">
-        <v>45951.6496180556</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B1615" t="n">
         <v>35000</v>
       </c>
       <c r="C1615" t="n">
-        <v>2.26999998092651</v>
+        <v>2.27999997138977</v>
       </c>
       <c r="D1615" t="n">
         <v>2.25999999046326</v>
@@ -43775,6 +43775,32 @@
         <v>320</v>
       </c>
       <c r="H1615" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="1" t="n">
+        <v>45952.6430671296</v>
+      </c>
+      <c r="B1616" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C1616" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D1616" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="E1616" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="F1616" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="G1616" t="s">
+        <v>311</v>
+      </c>
+      <c r="H1616" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43780,7 +43780,7 @@
     </row>
     <row r="1616">
       <c r="A1616" s="1" t="n">
-        <v>45952.6430671296</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B1616" t="n">
         <v>28000</v>
@@ -43801,6 +43801,32 @@
         <v>311</v>
       </c>
       <c r="H1616" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="1" t="n">
+        <v>45953.6494328704</v>
+      </c>
+      <c r="B1617" t="n">
+        <v>566000</v>
+      </c>
+      <c r="C1617" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="D1617" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="E1617" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="F1617" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="G1617" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1617" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43806,7 +43806,7 @@
     </row>
     <row r="1617">
       <c r="A1617" s="1" t="n">
-        <v>45953.6494328704</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B1617" t="n">
         <v>566000</v>
@@ -43827,6 +43827,32 @@
         <v>191</v>
       </c>
       <c r="H1617" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="1" t="n">
+        <v>45954.6495949074</v>
+      </c>
+      <c r="B1618" t="n">
+        <v>343000</v>
+      </c>
+      <c r="C1618" t="n">
+        <v>2.80999994277954</v>
+      </c>
+      <c r="D1618" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="E1618" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="F1618" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="G1618" t="s">
+        <v>187</v>
+      </c>
+      <c r="H1618" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43832,7 +43832,7 @@
     </row>
     <row r="1618">
       <c r="A1618" s="1" t="n">
-        <v>45954.6495949074</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B1618" t="n">
         <v>343000</v>
@@ -43853,6 +43853,32 @@
         <v>187</v>
       </c>
       <c r="H1618" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="1" t="n">
+        <v>45957.6912384259</v>
+      </c>
+      <c r="B1619" t="n">
+        <v>253000</v>
+      </c>
+      <c r="C1619" t="n">
+        <v>2.86999988555908</v>
+      </c>
+      <c r="D1619" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="E1619" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="F1619" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="G1619" t="s">
+        <v>181</v>
+      </c>
+      <c r="H1619" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43858,7 +43858,7 @@
     </row>
     <row r="1619">
       <c r="A1619" s="1" t="n">
-        <v>45957.6912384259</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B1619" t="n">
         <v>253000</v>
@@ -43879,6 +43879,32 @@
         <v>181</v>
       </c>
       <c r="H1619" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="1" t="n">
+        <v>45958.6912615741</v>
+      </c>
+      <c r="B1620" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C1620" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="D1620" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="E1620" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="F1620" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="G1620" t="s">
+        <v>308</v>
+      </c>
+      <c r="H1620" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="481">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1452,6 +1452,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.98500001430511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75999999046326</t>
   </si>
 </sst>
 </file>
@@ -43884,7 +43887,7 @@
     </row>
     <row r="1620">
       <c r="A1620" s="1" t="n">
-        <v>45958.6912615741</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B1620" t="n">
         <v>41000</v>
@@ -43905,6 +43908,32 @@
         <v>308</v>
       </c>
       <c r="H1620" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="1" t="n">
+        <v>45959.6868287037</v>
+      </c>
+      <c r="B1621" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C1621" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="D1621" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E1621" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F1621" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="G1621" t="s">
+        <v>480</v>
+      </c>
+      <c r="H1621" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43913,7 +43913,7 @@
     </row>
     <row r="1621">
       <c r="A1621" s="1" t="n">
-        <v>45959.6868287037</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B1621" t="n">
         <v>85000</v>
@@ -43934,6 +43934,32 @@
         <v>480</v>
       </c>
       <c r="H1621" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="1" t="n">
+        <v>45960.6809490741</v>
+      </c>
+      <c r="B1622" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C1622" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="D1622" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="E1622" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F1622" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="G1622" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1622" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43939,7 +43939,7 @@
     </row>
     <row r="1622">
       <c r="A1622" s="1" t="n">
-        <v>45960.6809490741</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B1622" t="n">
         <v>23000</v>
@@ -43960,6 +43960,32 @@
         <v>193</v>
       </c>
       <c r="H1622" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="1" t="n">
+        <v>45961.6783564815</v>
+      </c>
+      <c r="B1623" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1623" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="D1623" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="E1623" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F1623" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="G1623" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1623" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43965,7 +43965,7 @@
     </row>
     <row r="1623">
       <c r="A1623" s="1" t="n">
-        <v>45961.6783564815</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B1623" t="n">
         <v>9000</v>
@@ -43986,6 +43986,32 @@
         <v>197</v>
       </c>
       <c r="H1623" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="1" t="n">
+        <v>45964.6417592593</v>
+      </c>
+      <c r="B1624" t="n">
+        <v>17000</v>
+      </c>
+      <c r="C1624" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="D1624" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="E1624" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F1624" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="G1624" t="s">
+        <v>199</v>
+      </c>
+      <c r="H1624" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -43991,7 +43991,7 @@
     </row>
     <row r="1624">
       <c r="A1624" s="1" t="n">
-        <v>45964.6417592593</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B1624" t="n">
         <v>17000</v>
@@ -44012,6 +44012,32 @@
         <v>199</v>
       </c>
       <c r="H1624" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="1" t="n">
+        <v>45965.6629976852</v>
+      </c>
+      <c r="B1625" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C1625" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="D1625" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E1625" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F1625" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="G1625" t="s">
+        <v>199</v>
+      </c>
+      <c r="H1625" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44017,7 +44017,7 @@
     </row>
     <row r="1625">
       <c r="A1625" s="1" t="n">
-        <v>45965.6629976852</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B1625" t="n">
         <v>15000</v>
@@ -44038,6 +44038,32 @@
         <v>199</v>
       </c>
       <c r="H1625" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="1" t="n">
+        <v>45966.4496759259</v>
+      </c>
+      <c r="B1626" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1626" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D1626" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="E1626" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F1626" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="G1626" t="s">
+        <v>201</v>
+      </c>
+      <c r="H1626" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44043,25 +44043,25 @@
     </row>
     <row r="1626">
       <c r="A1626" s="1" t="n">
-        <v>45966.4496759259</v>
+        <v>45967.6281134259</v>
       </c>
       <c r="B1626" t="n">
-        <v>6000</v>
+        <v>14000</v>
       </c>
       <c r="C1626" t="n">
-        <v>2.70000004768372</v>
+        <v>2.69000005722046</v>
       </c>
       <c r="D1626" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E1626" t="n">
         <v>2.67000007629395</v>
       </c>
-      <c r="E1626" t="n">
-        <v>2.70000004768372</v>
-      </c>
       <c r="F1626" t="n">
-        <v>2.70000004768372</v>
+        <v>2.66000008583069</v>
       </c>
       <c r="G1626" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44043,25 +44043,25 @@
     </row>
     <row r="1626">
       <c r="A1626" s="1" t="n">
-        <v>45967.6281134259</v>
+        <v>45968.5791087963</v>
       </c>
       <c r="B1626" t="n">
-        <v>14000</v>
+        <v>22000</v>
       </c>
       <c r="C1626" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="D1626" t="n">
         <v>2.69000005722046</v>
       </c>
-      <c r="D1626" t="n">
-        <v>2.66000008583069</v>
-      </c>
       <c r="E1626" t="n">
-        <v>2.67000007629395</v>
+        <v>2.69000005722046</v>
       </c>
       <c r="F1626" t="n">
-        <v>2.66000008583069</v>
+        <v>2.71000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="482">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1455,6 +1455,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.75999999046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67000007629395</t>
   </si>
 </sst>
 </file>
@@ -44043,27 +44046,105 @@
     </row>
     <row r="1626">
       <c r="A1626" s="1" t="n">
-        <v>45968.5791087963</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B1626" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1626" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D1626" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="E1626" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F1626" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="G1626" t="s">
+        <v>201</v>
+      </c>
+      <c r="H1626" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B1627" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C1627" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D1627" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E1627" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="F1627" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G1627" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1627" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B1628" t="n">
         <v>22000</v>
       </c>
-      <c r="C1626" t="n">
+      <c r="C1628" t="n">
         <v>2.73000001907349</v>
       </c>
-      <c r="D1626" t="n">
+      <c r="D1628" t="n">
         <v>2.69000005722046</v>
       </c>
-      <c r="E1626" t="n">
+      <c r="E1628" t="n">
         <v>2.69000005722046</v>
       </c>
-      <c r="F1626" t="n">
+      <c r="F1628" t="n">
         <v>2.71000003814697</v>
       </c>
-      <c r="G1626" t="s">
+      <c r="G1628" t="s">
         <v>199</v>
       </c>
-      <c r="H1626" t="s">
+      <c r="H1628" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="1" t="n">
+        <v>45971.6653009259</v>
+      </c>
+      <c r="B1629" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C1629" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D1629" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="E1629" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F1629" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="G1629" t="s">
+        <v>481</v>
+      </c>
+      <c r="H1629" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44124,7 +44124,7 @@
     </row>
     <row r="1629">
       <c r="A1629" s="1" t="n">
-        <v>45971.6653009259</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B1629" t="n">
         <v>35000</v>
@@ -44145,6 +44145,32 @@
         <v>481</v>
       </c>
       <c r="H1629" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="1" t="n">
+        <v>45972.6801041667</v>
+      </c>
+      <c r="B1630" t="n">
+        <v>109000</v>
+      </c>
+      <c r="C1630" t="n">
+        <v>2.82999992370605</v>
+      </c>
+      <c r="D1630" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E1630" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="F1630" t="n">
+        <v>2.82999992370605</v>
+      </c>
+      <c r="G1630" t="s">
+        <v>176</v>
+      </c>
+      <c r="H1630" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44150,7 +44150,7 @@
     </row>
     <row r="1630">
       <c r="A1630" s="1" t="n">
-        <v>45972.6801041667</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B1630" t="n">
         <v>109000</v>
@@ -44171,6 +44171,32 @@
         <v>176</v>
       </c>
       <c r="H1630" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="1" t="n">
+        <v>45973.6232291667</v>
+      </c>
+      <c r="B1631" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C1631" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="D1631" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="E1631" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="F1631" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G1631" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1631" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44176,7 +44176,7 @@
     </row>
     <row r="1631">
       <c r="A1631" s="1" t="n">
-        <v>45973.6232291667</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B1631" t="n">
         <v>14000</v>
@@ -44197,6 +44197,32 @@
         <v>202</v>
       </c>
       <c r="H1631" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="1" t="n">
+        <v>45974.6910300926</v>
+      </c>
+      <c r="B1632" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C1632" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D1632" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="E1632" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="F1632" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="G1632" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1632" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44202,7 +44202,7 @@
     </row>
     <row r="1632">
       <c r="A1632" s="1" t="n">
-        <v>45974.6910300926</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B1632" t="n">
         <v>21000</v>
@@ -44223,6 +44223,32 @@
         <v>193</v>
       </c>
       <c r="H1632" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="1" t="n">
+        <v>45975.6690625</v>
+      </c>
+      <c r="B1633" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C1633" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D1633" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="E1633" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F1633" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="G1633" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1633" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44228,7 +44228,7 @@
     </row>
     <row r="1633">
       <c r="A1633" s="1" t="n">
-        <v>45975.6690625</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B1633" t="n">
         <v>12000</v>
@@ -44249,6 +44249,32 @@
         <v>197</v>
       </c>
       <c r="H1633" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" s="1" t="n">
+        <v>45978.6910300926</v>
+      </c>
+      <c r="B1634" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C1634" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="D1634" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="E1634" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F1634" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="G1634" t="s">
+        <v>481</v>
+      </c>
+      <c r="H1634" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44254,7 +44254,7 @@
     </row>
     <row r="1634">
       <c r="A1634" s="1" t="n">
-        <v>45978.6910300926</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B1634" t="n">
         <v>12000</v>
@@ -44275,6 +44275,32 @@
         <v>481</v>
       </c>
       <c r="H1634" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="1" t="n">
+        <v>45979.6910763889</v>
+      </c>
+      <c r="B1635" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C1635" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="D1635" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="E1635" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="F1635" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="G1635" t="s">
+        <v>481</v>
+      </c>
+      <c r="H1635" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44280,7 +44280,7 @@
     </row>
     <row r="1635">
       <c r="A1635" s="1" t="n">
-        <v>45979.6910763889</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B1635" t="n">
         <v>7000</v>
@@ -44301,6 +44301,32 @@
         <v>481</v>
       </c>
       <c r="H1635" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="1" t="n">
+        <v>45980.6412037037</v>
+      </c>
+      <c r="B1636" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C1636" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D1636" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="E1636" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F1636" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G1636" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1636" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44306,7 +44306,7 @@
     </row>
     <row r="1636">
       <c r="A1636" s="1" t="n">
-        <v>45980.6412037037</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B1636" t="n">
         <v>7000</v>
@@ -44327,6 +44327,32 @@
         <v>196</v>
       </c>
       <c r="H1636" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="1" t="n">
+        <v>45981.4805902778</v>
+      </c>
+      <c r="B1637" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1637" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D1637" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E1637" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F1637" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G1637" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1637" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44332,7 +44332,7 @@
     </row>
     <row r="1637">
       <c r="A1637" s="1" t="n">
-        <v>45981.4805902778</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B1637" t="n">
         <v>1000</v>
@@ -44353,6 +44353,32 @@
         <v>196</v>
       </c>
       <c r="H1637" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" s="1" t="n">
+        <v>45982.5888657407</v>
+      </c>
+      <c r="B1638" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1638" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="D1638" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="E1638" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="F1638" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="G1638" t="s">
+        <v>309</v>
+      </c>
+      <c r="H1638" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44358,7 +44358,7 @@
     </row>
     <row r="1638">
       <c r="A1638" s="1" t="n">
-        <v>45982.5888657407</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B1638" t="n">
         <v>4000</v>
@@ -44379,6 +44379,32 @@
         <v>309</v>
       </c>
       <c r="H1638" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="1" t="n">
+        <v>45985.6384490741</v>
+      </c>
+      <c r="B1639" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C1639" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="D1639" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E1639" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="F1639" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G1639" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1639" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44384,7 +44384,7 @@
     </row>
     <row r="1639">
       <c r="A1639" s="1" t="n">
-        <v>45985.6384490741</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B1639" t="n">
         <v>10000</v>
@@ -44405,6 +44405,32 @@
         <v>194</v>
       </c>
       <c r="H1639" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="1" t="n">
+        <v>45986.6330902778</v>
+      </c>
+      <c r="B1640" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C1640" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D1640" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E1640" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F1640" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G1640" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1640" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44410,7 +44410,7 @@
     </row>
     <row r="1640">
       <c r="A1640" s="1" t="n">
-        <v>45986.6330902778</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B1640" t="n">
         <v>16000</v>
@@ -44431,6 +44431,32 @@
         <v>196</v>
       </c>
       <c r="H1640" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="1" t="n">
+        <v>45987.5594097222</v>
+      </c>
+      <c r="B1641" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1641" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="D1641" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E1641" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="F1641" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="G1641" t="s">
+        <v>309</v>
+      </c>
+      <c r="H1641" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44436,7 +44436,7 @@
     </row>
     <row r="1641">
       <c r="A1641" s="1" t="n">
-        <v>45987.5594097222</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B1641" t="n">
         <v>8000</v>
@@ -44457,6 +44457,32 @@
         <v>309</v>
       </c>
       <c r="H1641" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="1" t="n">
+        <v>45988.6546875</v>
+      </c>
+      <c r="B1642" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1642" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="D1642" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="E1642" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="F1642" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="G1642" t="s">
+        <v>309</v>
+      </c>
+      <c r="H1642" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44462,7 +44462,7 @@
     </row>
     <row r="1642">
       <c r="A1642" s="1" t="n">
-        <v>45988.6546875</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B1642" t="n">
         <v>3000</v>
@@ -44483,6 +44483,32 @@
         <v>309</v>
       </c>
       <c r="H1642" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="1" t="n">
+        <v>45989.6912384259</v>
+      </c>
+      <c r="B1643" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C1643" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="D1643" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E1643" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="F1643" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G1643" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1643" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44488,7 +44488,7 @@
     </row>
     <row r="1643">
       <c r="A1643" s="1" t="n">
-        <v>45989.6912384259</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B1643" t="n">
         <v>41000</v>
@@ -44509,6 +44509,32 @@
         <v>196</v>
       </c>
       <c r="H1643" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="1" t="n">
+        <v>45992.6353472222</v>
+      </c>
+      <c r="B1644" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C1644" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D1644" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E1644" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F1644" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G1644" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1644" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44514,7 +44514,7 @@
     </row>
     <row r="1644">
       <c r="A1644" s="1" t="n">
-        <v>45992.6353472222</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B1644" t="n">
         <v>7000</v>
@@ -44535,6 +44535,32 @@
         <v>196</v>
       </c>
       <c r="H1644" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="1" t="n">
+        <v>45993.6742013889</v>
+      </c>
+      <c r="B1645" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C1645" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D1645" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E1645" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F1645" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="G1645" t="s">
+        <v>309</v>
+      </c>
+      <c r="H1645" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44540,7 +44540,7 @@
     </row>
     <row r="1645">
       <c r="A1645" s="1" t="n">
-        <v>45993.6742013889</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B1645" t="n">
         <v>14000</v>
@@ -44561,6 +44561,32 @@
         <v>309</v>
       </c>
       <c r="H1645" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="1" t="n">
+        <v>45994.6911458333</v>
+      </c>
+      <c r="B1646" t="n">
+        <v>19000</v>
+      </c>
+      <c r="C1646" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="D1646" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E1646" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="F1646" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G1646" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1646" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44566,7 +44566,7 @@
     </row>
     <row r="1646">
       <c r="A1646" s="1" t="n">
-        <v>45994.6911458333</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B1646" t="n">
         <v>19000</v>
@@ -44587,6 +44587,32 @@
         <v>194</v>
       </c>
       <c r="H1646" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="1" t="n">
+        <v>45995.6775694444</v>
+      </c>
+      <c r="B1647" t="n">
+        <v>81000</v>
+      </c>
+      <c r="C1647" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="D1647" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="E1647" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F1647" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G1647" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1647" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44592,7 +44592,7 @@
     </row>
     <row r="1647">
       <c r="A1647" s="1" t="n">
-        <v>45995.6775694444</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B1647" t="n">
         <v>81000</v>
@@ -44613,6 +44613,32 @@
         <v>194</v>
       </c>
       <c r="H1647" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="1" t="n">
+        <v>45996.6763310185</v>
+      </c>
+      <c r="B1648" t="n">
+        <v>33000</v>
+      </c>
+      <c r="C1648" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="D1648" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="E1648" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F1648" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="G1648" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1648" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44618,7 +44618,7 @@
     </row>
     <row r="1648">
       <c r="A1648" s="1" t="n">
-        <v>45996.6763310185</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B1648" t="n">
         <v>33000</v>
@@ -44639,6 +44639,32 @@
         <v>191</v>
       </c>
       <c r="H1648" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="1" t="n">
+        <v>45999.6578009259</v>
+      </c>
+      <c r="B1649" t="n">
+        <v>207000</v>
+      </c>
+      <c r="C1649" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="D1649" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="E1649" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="F1649" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G1649" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1649" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44644,7 +44644,7 @@
     </row>
     <row r="1649">
       <c r="A1649" s="1" t="n">
-        <v>45999.6578009259</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B1649" t="n">
         <v>207000</v>
@@ -44665,6 +44665,32 @@
         <v>194</v>
       </c>
       <c r="H1649" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="1" t="n">
+        <v>46000.6782060185</v>
+      </c>
+      <c r="B1650" t="n">
+        <v>183000</v>
+      </c>
+      <c r="C1650" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="D1650" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="E1650" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="F1650" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G1650" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1650" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44670,7 +44670,7 @@
     </row>
     <row r="1650">
       <c r="A1650" s="1" t="n">
-        <v>46000.6782060185</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B1650" t="n">
         <v>183000</v>
@@ -44691,6 +44691,32 @@
         <v>194</v>
       </c>
       <c r="H1650" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="1" t="n">
+        <v>46001.6742476852</v>
+      </c>
+      <c r="B1651" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C1651" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="D1651" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="E1651" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="F1651" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="G1651" t="s">
+        <v>189</v>
+      </c>
+      <c r="H1651" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44696,7 +44696,7 @@
     </row>
     <row r="1651">
       <c r="A1651" s="1" t="n">
-        <v>46001.6742476852</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B1651" t="n">
         <v>24000</v>
@@ -44717,6 +44717,32 @@
         <v>189</v>
       </c>
       <c r="H1651" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="1" t="n">
+        <v>46002.6911111111</v>
+      </c>
+      <c r="B1652" t="n">
+        <v>192000</v>
+      </c>
+      <c r="C1652" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D1652" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="E1652" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F1652" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G1652" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1652" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44722,7 +44722,7 @@
     </row>
     <row r="1652">
       <c r="A1652" s="1" t="n">
-        <v>46002.6911111111</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B1652" t="n">
         <v>192000</v>
@@ -44743,6 +44743,32 @@
         <v>196</v>
       </c>
       <c r="H1652" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="1" t="n">
+        <v>46003.6848958333</v>
+      </c>
+      <c r="B1653" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C1653" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="D1653" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E1653" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="F1653" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G1653" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1653" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44748,7 +44748,7 @@
     </row>
     <row r="1653">
       <c r="A1653" s="1" t="n">
-        <v>46003.6848958333</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B1653" t="n">
         <v>25000</v>
@@ -44769,6 +44769,32 @@
         <v>196</v>
       </c>
       <c r="H1653" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="1" t="n">
+        <v>46006.6912962963</v>
+      </c>
+      <c r="B1654" t="n">
+        <v>202000</v>
+      </c>
+      <c r="C1654" t="n">
+        <v>2.95000004768372</v>
+      </c>
+      <c r="D1654" t="n">
+        <v>2.89000010490417</v>
+      </c>
+      <c r="E1654" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F1654" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="G1654" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1654" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44774,7 +44774,7 @@
     </row>
     <row r="1654">
       <c r="A1654" s="1" t="n">
-        <v>46006.6912962963</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B1654" t="n">
         <v>202000</v>
@@ -44795,6 +44795,32 @@
         <v>158</v>
       </c>
       <c r="H1654" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="1" t="n">
+        <v>46007.6434259259</v>
+      </c>
+      <c r="B1655" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C1655" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="D1655" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="E1655" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F1655" t="n">
+        <v>2.91000008583069</v>
+      </c>
+      <c r="G1655" t="s">
+        <v>182</v>
+      </c>
+      <c r="H1655" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44800,7 +44800,7 @@
     </row>
     <row r="1655">
       <c r="A1655" s="1" t="n">
-        <v>46007.6434259259</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B1655" t="n">
         <v>41000</v>
@@ -44821,6 +44821,32 @@
         <v>182</v>
       </c>
       <c r="H1655" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="1" t="n">
+        <v>46008.6911111111</v>
+      </c>
+      <c r="B1656" t="n">
+        <v>55000</v>
+      </c>
+      <c r="C1656" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="D1656" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="E1656" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F1656" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="G1656" t="s">
+        <v>174</v>
+      </c>
+      <c r="H1656" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44826,7 +44826,7 @@
     </row>
     <row r="1656">
       <c r="A1656" s="1" t="n">
-        <v>46008.6911111111</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B1656" t="n">
         <v>55000</v>
@@ -44847,6 +44847,32 @@
         <v>174</v>
       </c>
       <c r="H1656" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="1" t="n">
+        <v>46009.6143634259</v>
+      </c>
+      <c r="B1657" t="n">
+        <v>32000</v>
+      </c>
+      <c r="C1657" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="D1657" t="n">
+        <v>2.91000008583069</v>
+      </c>
+      <c r="E1657" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F1657" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="G1657" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1657" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44852,7 +44852,7 @@
     </row>
     <row r="1657">
       <c r="A1657" s="1" t="n">
-        <v>46009.6143634259</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B1657" t="n">
         <v>32000</v>
@@ -44873,6 +44873,32 @@
         <v>158</v>
       </c>
       <c r="H1657" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="1" t="n">
+        <v>46010.6558101852</v>
+      </c>
+      <c r="B1658" t="n">
+        <v>29000</v>
+      </c>
+      <c r="C1658" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="D1658" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="E1658" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F1658" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="G1658" t="s">
+        <v>161</v>
+      </c>
+      <c r="H1658" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44878,7 +44878,7 @@
     </row>
     <row r="1658">
       <c r="A1658" s="1" t="n">
-        <v>46010.6558101852</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B1658" t="n">
         <v>29000</v>
@@ -44899,6 +44899,32 @@
         <v>161</v>
       </c>
       <c r="H1658" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="1" t="n">
+        <v>46013.6649884259</v>
+      </c>
+      <c r="B1659" t="n">
+        <v>88000</v>
+      </c>
+      <c r="C1659" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="D1659" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="E1659" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F1659" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="G1659" t="s">
+        <v>173</v>
+      </c>
+      <c r="H1659" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44904,7 +44904,7 @@
     </row>
     <row r="1659">
       <c r="A1659" s="1" t="n">
-        <v>46013.6649884259</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B1659" t="n">
         <v>88000</v>
@@ -44925,6 +44925,32 @@
         <v>173</v>
       </c>
       <c r="H1659" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="1" t="n">
+        <v>46014.6800578704</v>
+      </c>
+      <c r="B1660" t="n">
+        <v>94000</v>
+      </c>
+      <c r="C1660" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="D1660" t="n">
+        <v>2.91000008583069</v>
+      </c>
+      <c r="E1660" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F1660" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="G1660" t="s">
+        <v>161</v>
+      </c>
+      <c r="H1660" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44930,7 +44930,7 @@
     </row>
     <row r="1660">
       <c r="A1660" s="1" t="n">
-        <v>46014.6800578704</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B1660" t="n">
         <v>94000</v>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44954,6 +44954,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1661">
+      <c r="A1661" s="1" t="n">
+        <v>46020.691712963</v>
+      </c>
+      <c r="B1661" t="n">
+        <v>290000</v>
+      </c>
+      <c r="C1661" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="D1661" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="E1661" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="F1661" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="G1661" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1661" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44956,7 +44956,7 @@
     </row>
     <row r="1661">
       <c r="A1661" s="1" t="n">
-        <v>46020.691712963</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B1661" t="n">
         <v>290000</v>
@@ -44977,6 +44977,32 @@
         <v>146</v>
       </c>
       <c r="H1661" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="1" t="n">
+        <v>46021.6909837963</v>
+      </c>
+      <c r="B1662" t="n">
+        <v>216000</v>
+      </c>
+      <c r="C1662" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1662" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="E1662" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="F1662" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1662" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1662" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -44982,7 +44982,7 @@
     </row>
     <row r="1662">
       <c r="A1662" s="1" t="n">
-        <v>46021.6909837963</v>
+        <v>46021.3333333333</v>
       </c>
       <c r="B1662" t="n">
         <v>216000</v>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45006,6 +45006,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1663">
+      <c r="A1663" s="1" t="n">
+        <v>46024.6839814815</v>
+      </c>
+      <c r="B1663" t="n">
+        <v>183000</v>
+      </c>
+      <c r="C1663" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="D1663" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="E1663" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1663" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1663" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1663" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45008,7 +45008,7 @@
     </row>
     <row r="1663">
       <c r="A1663" s="1" t="n">
-        <v>46024.6839814815</v>
+        <v>46024.3333333333</v>
       </c>
       <c r="B1663" t="n">
         <v>183000</v>
@@ -45029,6 +45029,32 @@
         <v>166</v>
       </c>
       <c r="H1663" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="1" t="n">
+        <v>46027.6909722222</v>
+      </c>
+      <c r="B1664" t="n">
+        <v>136000</v>
+      </c>
+      <c r="C1664" t="n">
+        <v>3.33999991416931</v>
+      </c>
+      <c r="D1664" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1664" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1664" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1664" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1664" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45034,7 +45034,7 @@
     </row>
     <row r="1664">
       <c r="A1664" s="1" t="n">
-        <v>46027.6909722222</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B1664" t="n">
         <v>136000</v>
@@ -45055,6 +45055,32 @@
         <v>212</v>
       </c>
       <c r="H1664" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="1" t="n">
+        <v>46028.6134606482</v>
+      </c>
+      <c r="B1665" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C1665" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="D1665" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="E1665" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="F1665" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="G1665" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1665" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45060,7 +45060,7 @@
     </row>
     <row r="1665">
       <c r="A1665" s="1" t="n">
-        <v>46028.6134606482</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B1665" t="n">
         <v>11000</v>
@@ -45081,6 +45081,32 @@
         <v>147</v>
       </c>
       <c r="H1665" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="1" t="n">
+        <v>46029.6911689815</v>
+      </c>
+      <c r="B1666" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C1666" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1666" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="E1666" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F1666" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1666" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1666" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45086,7 +45086,7 @@
     </row>
     <row r="1666">
       <c r="A1666" s="1" t="n">
-        <v>46029.6911689815</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B1666" t="n">
         <v>7000</v>
@@ -45095,7 +45095,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="D1666" t="n">
-        <v>3.20000004768372</v>
+        <v>3.19000005722046</v>
       </c>
       <c r="E1666" t="n">
         <v>3.20000004768372</v>
@@ -45107,6 +45107,32 @@
         <v>204</v>
       </c>
       <c r="H1666" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="1" t="n">
+        <v>46030.6746643519</v>
+      </c>
+      <c r="B1667" t="n">
+        <v>54000</v>
+      </c>
+      <c r="C1667" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1667" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1667" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1667" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1667" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1667" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45112,7 +45112,7 @@
     </row>
     <row r="1667">
       <c r="A1667" s="1" t="n">
-        <v>46030.6746643519</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B1667" t="n">
         <v>54000</v>
@@ -45133,6 +45133,32 @@
         <v>204</v>
       </c>
       <c r="H1667" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="1" t="n">
+        <v>46031.4613310185</v>
+      </c>
+      <c r="B1668" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C1668" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="D1668" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1668" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1668" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1668" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1668" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45138,7 +45138,7 @@
     </row>
     <row r="1668">
       <c r="A1668" s="1" t="n">
-        <v>46031.4613310185</v>
+        <v>46031.3333333333</v>
       </c>
       <c r="B1668" t="n">
         <v>5000</v>
@@ -45159,6 +45159,32 @@
         <v>166</v>
       </c>
       <c r="H1668" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="1" t="n">
+        <v>46034.6467592593</v>
+      </c>
+      <c r="B1669" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1669" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1669" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1669" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F1669" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1669" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1669" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45164,7 +45164,7 @@
     </row>
     <row r="1669">
       <c r="A1669" s="1" t="n">
-        <v>46034.6467592593</v>
+        <v>46034.3333333333</v>
       </c>
       <c r="B1669" t="n">
         <v>8000</v>
@@ -45185,6 +45185,32 @@
         <v>204</v>
       </c>
       <c r="H1669" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="1" t="n">
+        <v>46035.6205324074</v>
+      </c>
+      <c r="B1670" t="n">
+        <v>109000</v>
+      </c>
+      <c r="C1670" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1670" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1670" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1670" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1670" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1670" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45190,7 +45190,7 @@
     </row>
     <row r="1670">
       <c r="A1670" s="1" t="n">
-        <v>46035.6205324074</v>
+        <v>46035.3333333333</v>
       </c>
       <c r="B1670" t="n">
         <v>109000</v>
@@ -45211,6 +45211,32 @@
         <v>204</v>
       </c>
       <c r="H1670" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="1" t="n">
+        <v>46036.6817013889</v>
+      </c>
+      <c r="B1671" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1671" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1671" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1671" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1671" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1671" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1671" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45216,7 +45216,7 @@
     </row>
     <row r="1671">
       <c r="A1671" s="1" t="n">
-        <v>46036.6817013889</v>
+        <v>46036.3333333333</v>
       </c>
       <c r="B1671" t="n">
         <v>2000</v>
@@ -45237,6 +45237,32 @@
         <v>204</v>
       </c>
       <c r="H1671" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="1" t="n">
+        <v>46037.619537037</v>
+      </c>
+      <c r="B1672" t="n">
+        <v>26000</v>
+      </c>
+      <c r="C1672" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1672" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1672" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1672" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1672" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1672" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45242,7 +45242,7 @@
     </row>
     <row r="1672">
       <c r="A1672" s="1" t="n">
-        <v>46037.619537037</v>
+        <v>46037.3333333333</v>
       </c>
       <c r="B1672" t="n">
         <v>26000</v>
@@ -45263,6 +45263,32 @@
         <v>166</v>
       </c>
       <c r="H1672" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="1" t="n">
+        <v>46038.6831944444</v>
+      </c>
+      <c r="B1673" t="n">
+        <v>55000</v>
+      </c>
+      <c r="C1673" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1673" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1673" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1673" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1673" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1673" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45268,7 +45268,7 @@
     </row>
     <row r="1673">
       <c r="A1673" s="1" t="n">
-        <v>46038.6831944444</v>
+        <v>46038.3333333333</v>
       </c>
       <c r="B1673" t="n">
         <v>55000</v>
@@ -45289,6 +45289,32 @@
         <v>166</v>
       </c>
       <c r="H1673" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="1" t="n">
+        <v>46041.6910763889</v>
+      </c>
+      <c r="B1674" t="n">
+        <v>26000</v>
+      </c>
+      <c r="C1674" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="D1674" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1674" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1674" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1674" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1674" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45294,7 +45294,7 @@
     </row>
     <row r="1674">
       <c r="A1674" s="1" t="n">
-        <v>46041.6910763889</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B1674" t="n">
         <v>26000</v>
@@ -45315,6 +45315,32 @@
         <v>166</v>
       </c>
       <c r="H1674" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="1" t="n">
+        <v>46042.691099537</v>
+      </c>
+      <c r="B1675" t="n">
+        <v>190000</v>
+      </c>
+      <c r="C1675" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1675" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="E1675" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1675" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="G1675" t="s">
+        <v>205</v>
+      </c>
+      <c r="H1675" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45320,13 +45320,13 @@
     </row>
     <row r="1675">
       <c r="A1675" s="1" t="n">
-        <v>46042.691099537</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B1675" t="n">
         <v>190000</v>
       </c>
       <c r="C1675" t="n">
-        <v>3.20000004768372</v>
+        <v>3.22000002861023</v>
       </c>
       <c r="D1675" t="n">
         <v>3.17000007629395</v>
@@ -45341,6 +45341,32 @@
         <v>205</v>
       </c>
       <c r="H1675" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="1" t="n">
+        <v>46043.6681828704</v>
+      </c>
+      <c r="B1676" t="n">
+        <v>193000</v>
+      </c>
+      <c r="C1676" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1676" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1676" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1676" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1676" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1676" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45346,7 +45346,7 @@
     </row>
     <row r="1676">
       <c r="A1676" s="1" t="n">
-        <v>46043.6681828704</v>
+        <v>46043.3333333333</v>
       </c>
       <c r="B1676" t="n">
         <v>193000</v>
@@ -45367,6 +45367,32 @@
         <v>212</v>
       </c>
       <c r="H1676" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="1" t="n">
+        <v>46044.6822222222</v>
+      </c>
+      <c r="B1677" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1677" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1677" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1677" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1677" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1677" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1677" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45372,7 +45372,7 @@
     </row>
     <row r="1677">
       <c r="A1677" s="1" t="n">
-        <v>46044.6822222222</v>
+        <v>46044.3333333333</v>
       </c>
       <c r="B1677" t="n">
         <v>2000</v>
@@ -45393,6 +45393,32 @@
         <v>204</v>
       </c>
       <c r="H1677" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="1" t="n">
+        <v>46045.5974074074</v>
+      </c>
+      <c r="B1678" t="n">
+        <v>102000</v>
+      </c>
+      <c r="C1678" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="D1678" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1678" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1678" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1678" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1678" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45398,7 +45398,7 @@
     </row>
     <row r="1678">
       <c r="A1678" s="1" t="n">
-        <v>46045.5974074074</v>
+        <v>46045.3333333333</v>
       </c>
       <c r="B1678" t="n">
         <v>102000</v>
@@ -45419,6 +45419,32 @@
         <v>212</v>
       </c>
       <c r="H1678" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="1" t="n">
+        <v>46048.68125</v>
+      </c>
+      <c r="B1679" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C1679" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1679" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1679" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1679" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1679" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1679" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45424,7 +45424,7 @@
     </row>
     <row r="1679">
       <c r="A1679" s="1" t="n">
-        <v>46048.68125</v>
+        <v>46048.3333333333</v>
       </c>
       <c r="B1679" t="n">
         <v>30000</v>
@@ -45445,6 +45445,32 @@
         <v>212</v>
       </c>
       <c r="H1679" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="1" t="n">
+        <v>46049.6739583333</v>
+      </c>
+      <c r="B1680" t="n">
+        <v>57000</v>
+      </c>
+      <c r="C1680" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1680" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1680" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1680" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1680" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1680" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45450,7 +45450,7 @@
     </row>
     <row r="1680">
       <c r="A1680" s="1" t="n">
-        <v>46049.6739583333</v>
+        <v>46049.3333333333</v>
       </c>
       <c r="B1680" t="n">
         <v>57000</v>
@@ -45471,6 +45471,32 @@
         <v>212</v>
       </c>
       <c r="H1680" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="1" t="n">
+        <v>46050.6912037037</v>
+      </c>
+      <c r="B1681" t="n">
+        <v>179000</v>
+      </c>
+      <c r="C1681" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1681" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="E1681" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1681" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1681" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1681" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45476,7 +45476,7 @@
     </row>
     <row r="1681">
       <c r="A1681" s="1" t="n">
-        <v>46050.6912037037</v>
+        <v>46050.3333333333</v>
       </c>
       <c r="B1681" t="n">
         <v>179000</v>
@@ -45497,6 +45497,32 @@
         <v>204</v>
       </c>
       <c r="H1681" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="1" t="n">
+        <v>46051.6611458333</v>
+      </c>
+      <c r="B1682" t="n">
+        <v>19000</v>
+      </c>
+      <c r="C1682" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1682" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1682" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1682" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1682" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1682" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45502,7 +45502,7 @@
     </row>
     <row r="1682">
       <c r="A1682" s="1" t="n">
-        <v>46051.6611458333</v>
+        <v>46051.3333333333</v>
       </c>
       <c r="B1682" t="n">
         <v>19000</v>
@@ -45523,6 +45523,32 @@
         <v>166</v>
       </c>
       <c r="H1682" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="1" t="n">
+        <v>46052.6038078704</v>
+      </c>
+      <c r="B1683" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C1683" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="D1683" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="E1683" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1683" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1683" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1683" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45528,13 +45528,13 @@
     </row>
     <row r="1683">
       <c r="A1683" s="1" t="n">
-        <v>46052.6038078704</v>
+        <v>46052.3333333333</v>
       </c>
       <c r="B1683" t="n">
-        <v>16000</v>
+        <v>29000</v>
       </c>
       <c r="C1683" t="n">
-        <v>3.1800000667572</v>
+        <v>3.19000005722046</v>
       </c>
       <c r="D1683" t="n">
         <v>3.17000007629395</v>
@@ -45543,12 +45543,38 @@
         <v>3.1800000667572</v>
       </c>
       <c r="F1683" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1683" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1683" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="1" t="n">
+        <v>46055.6914351852</v>
+      </c>
+      <c r="B1684" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C1684" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1684" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="G1683" t="s">
-        <v>166</v>
-      </c>
-      <c r="H1683" t="s">
+      <c r="E1684" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1684" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1684" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1684" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45554,7 +45554,7 @@
     </row>
     <row r="1684">
       <c r="A1684" s="1" t="n">
-        <v>46055.6914351852</v>
+        <v>46055.3333333333</v>
       </c>
       <c r="B1684" t="n">
         <v>40000</v>
@@ -45575,6 +45575,32 @@
         <v>204</v>
       </c>
       <c r="H1684" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="1" t="n">
+        <v>46056.6609027778</v>
+      </c>
+      <c r="B1685" t="n">
+        <v>75000</v>
+      </c>
+      <c r="C1685" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1685" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1685" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1685" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1685" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1685" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45580,7 +45580,7 @@
     </row>
     <row r="1685">
       <c r="A1685" s="1" t="n">
-        <v>46056.6609027778</v>
+        <v>46056.3333333333</v>
       </c>
       <c r="B1685" t="n">
         <v>75000</v>
@@ -45601,6 +45601,32 @@
         <v>212</v>
       </c>
       <c r="H1685" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="1" t="n">
+        <v>46057.6331134259</v>
+      </c>
+      <c r="B1686" t="n">
+        <v>82000</v>
+      </c>
+      <c r="C1686" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1686" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1686" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F1686" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1686" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1686" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45606,7 +45606,7 @@
     </row>
     <row r="1686">
       <c r="A1686" s="1" t="n">
-        <v>46057.6331134259</v>
+        <v>46057.3333333333</v>
       </c>
       <c r="B1686" t="n">
         <v>82000</v>
@@ -45627,6 +45627,32 @@
         <v>166</v>
       </c>
       <c r="H1686" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="1" t="n">
+        <v>46058.6113888889</v>
+      </c>
+      <c r="B1687" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1687" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="D1687" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1687" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1687" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1687" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1687" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45632,7 +45632,7 @@
     </row>
     <row r="1687">
       <c r="A1687" s="1" t="n">
-        <v>46058.6113888889</v>
+        <v>46058.3333333333</v>
       </c>
       <c r="B1687" t="n">
         <v>2000</v>
@@ -45653,6 +45653,32 @@
         <v>166</v>
       </c>
       <c r="H1687" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="1" t="n">
+        <v>46059.6424305556</v>
+      </c>
+      <c r="B1688" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1688" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="D1688" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="E1688" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1688" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="G1688" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1688" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45658,7 +45658,7 @@
     </row>
     <row r="1688">
       <c r="A1688" s="1" t="n">
-        <v>46059.6424305556</v>
+        <v>46059.3333333333</v>
       </c>
       <c r="B1688" t="n">
         <v>9000</v>
@@ -45679,6 +45679,32 @@
         <v>155</v>
       </c>
       <c r="H1688" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="1" t="n">
+        <v>46062.6782060185</v>
+      </c>
+      <c r="B1689" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1689" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="D1689" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="E1689" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="F1689" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="G1689" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1689" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45684,7 +45684,7 @@
     </row>
     <row r="1689">
       <c r="A1689" s="1" t="n">
-        <v>46062.6782060185</v>
+        <v>46062.3333333333</v>
       </c>
       <c r="B1689" t="n">
         <v>6000</v>
@@ -45705,6 +45705,32 @@
         <v>155</v>
       </c>
       <c r="H1689" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="1" t="n">
+        <v>46063.5085416667</v>
+      </c>
+      <c r="B1690" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1690" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="D1690" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="E1690" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="F1690" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="G1690" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1690" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45710,7 +45710,7 @@
     </row>
     <row r="1690">
       <c r="A1690" s="1" t="n">
-        <v>46063.5085416667</v>
+        <v>46063.3333333333</v>
       </c>
       <c r="B1690" t="n">
         <v>1000</v>
@@ -45731,6 +45731,32 @@
         <v>155</v>
       </c>
       <c r="H1690" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="1" t="n">
+        <v>46064.6283217593</v>
+      </c>
+      <c r="B1691" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1691" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="D1691" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1691" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1691" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1691" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1691" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45736,7 +45736,7 @@
     </row>
     <row r="1691">
       <c r="A1691" s="1" t="n">
-        <v>46064.6283217593</v>
+        <v>46064.3333333333</v>
       </c>
       <c r="B1691" t="n">
         <v>9000</v>
@@ -45757,6 +45757,32 @@
         <v>166</v>
       </c>
       <c r="H1691" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="1" t="n">
+        <v>46065.6912268518</v>
+      </c>
+      <c r="B1692" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C1692" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="D1692" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="E1692" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="F1692" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="G1692" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1692" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45762,7 +45762,7 @@
     </row>
     <row r="1692">
       <c r="A1692" s="1" t="n">
-        <v>46065.6912268518</v>
+        <v>46065.3333333333</v>
       </c>
       <c r="B1692" t="n">
         <v>60000</v>
@@ -45783,6 +45783,32 @@
         <v>155</v>
       </c>
       <c r="H1692" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="1" t="n">
+        <v>46066.6319328704</v>
+      </c>
+      <c r="B1693" t="n">
+        <v>113000</v>
+      </c>
+      <c r="C1693" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1693" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="E1693" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1693" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1693" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1693" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45788,7 +45788,7 @@
     </row>
     <row r="1693">
       <c r="A1693" s="1" t="n">
-        <v>46066.6319328704</v>
+        <v>46066.3333333333</v>
       </c>
       <c r="B1693" t="n">
         <v>113000</v>
@@ -45809,6 +45809,32 @@
         <v>166</v>
       </c>
       <c r="H1693" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="1" t="n">
+        <v>46069.4140277778</v>
+      </c>
+      <c r="B1694" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C1694" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1694" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1694" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1694" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1694" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1694" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45814,7 +45814,7 @@
     </row>
     <row r="1694">
       <c r="A1694" s="1" t="n">
-        <v>46069.4140277778</v>
+        <v>46069.3333333333</v>
       </c>
       <c r="B1694" t="n">
         <v>1000000</v>
@@ -45835,6 +45835,32 @@
         <v>204</v>
       </c>
       <c r="H1694" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="1" t="n">
+        <v>46070.663275463</v>
+      </c>
+      <c r="B1695" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C1695" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1695" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1695" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1695" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1695" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1695" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45840,7 +45840,7 @@
     </row>
     <row r="1695">
       <c r="A1695" s="1" t="n">
-        <v>46070.663275463</v>
+        <v>46070.3333333333</v>
       </c>
       <c r="B1695" t="n">
         <v>5000</v>
@@ -45861,6 +45861,32 @@
         <v>166</v>
       </c>
       <c r="H1695" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="1" t="n">
+        <v>46071.6788657407</v>
+      </c>
+      <c r="B1696" t="n">
+        <v>32000</v>
+      </c>
+      <c r="C1696" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1696" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="E1696" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1696" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1696" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1696" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45866,7 +45866,7 @@
     </row>
     <row r="1696">
       <c r="A1696" s="1" t="n">
-        <v>46071.6788657407</v>
+        <v>46071.3333333333</v>
       </c>
       <c r="B1696" t="n">
         <v>32000</v>
@@ -45887,6 +45887,32 @@
         <v>166</v>
       </c>
       <c r="H1696" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="1" t="n">
+        <v>46072.6912847222</v>
+      </c>
+      <c r="B1697" t="n">
+        <v>117000</v>
+      </c>
+      <c r="C1697" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="D1697" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1697" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1697" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="G1697" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1697" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45892,7 +45892,7 @@
     </row>
     <row r="1697">
       <c r="A1697" s="1" t="n">
-        <v>46072.6912847222</v>
+        <v>46072.3333333333</v>
       </c>
       <c r="B1697" t="n">
         <v>117000</v>
@@ -45913,6 +45913,32 @@
         <v>147</v>
       </c>
       <c r="H1697" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="1" t="n">
+        <v>46073.6911805556</v>
+      </c>
+      <c r="B1698" t="n">
+        <v>70000</v>
+      </c>
+      <c r="C1698" t="n">
+        <v>3.28999996185303</v>
+      </c>
+      <c r="D1698" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1698" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="F1698" t="n">
+        <v>3.28999996185303</v>
+      </c>
+      <c r="G1698" t="s">
+        <v>214</v>
+      </c>
+      <c r="H1698" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45918,7 +45918,7 @@
     </row>
     <row r="1698">
       <c r="A1698" s="1" t="n">
-        <v>46073.6911805556</v>
+        <v>46073.3333333333</v>
       </c>
       <c r="B1698" t="n">
         <v>70000</v>
@@ -45939,6 +45939,32 @@
         <v>214</v>
       </c>
       <c r="H1698" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="1" t="n">
+        <v>46076.677974537</v>
+      </c>
+      <c r="B1699" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1699" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="D1699" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="E1699" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="F1699" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="G1699" t="s">
+        <v>205</v>
+      </c>
+      <c r="H1699" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45944,7 +45944,7 @@
     </row>
     <row r="1699">
       <c r="A1699" s="1" t="n">
-        <v>46076.677974537</v>
+        <v>46076.3333333333</v>
       </c>
       <c r="B1699" t="n">
         <v>8000</v>
@@ -45965,6 +45965,32 @@
         <v>205</v>
       </c>
       <c r="H1699" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="1" t="n">
+        <v>46077.5597106481</v>
+      </c>
+      <c r="B1700" t="n">
+        <v>17000</v>
+      </c>
+      <c r="C1700" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1700" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1700" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F1700" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1700" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1700" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45970,7 +45970,7 @@
     </row>
     <row r="1700">
       <c r="A1700" s="1" t="n">
-        <v>46077.5597106481</v>
+        <v>46077.3333333333</v>
       </c>
       <c r="B1700" t="n">
         <v>17000</v>
@@ -45991,6 +45991,32 @@
         <v>212</v>
       </c>
       <c r="H1700" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="1" t="n">
+        <v>46078.6911574074</v>
+      </c>
+      <c r="B1701" t="n">
+        <v>148000</v>
+      </c>
+      <c r="C1701" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D1701" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1701" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1701" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="G1701" t="s">
+        <v>148</v>
+      </c>
+      <c r="H1701" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -45996,7 +45996,7 @@
     </row>
     <row r="1701">
       <c r="A1701" s="1" t="n">
-        <v>46078.6911574074</v>
+        <v>46078.3333333333</v>
       </c>
       <c r="B1701" t="n">
         <v>148000</v>
@@ -46017,6 +46017,32 @@
         <v>148</v>
       </c>
       <c r="H1701" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="1" t="n">
+        <v>46079.6910300926</v>
+      </c>
+      <c r="B1702" t="n">
+        <v>46000</v>
+      </c>
+      <c r="C1702" t="n">
+        <v>3.28999996185303</v>
+      </c>
+      <c r="D1702" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1702" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1702" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="G1702" t="s">
+        <v>148</v>
+      </c>
+      <c r="H1702" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46022,7 +46022,7 @@
     </row>
     <row r="1702">
       <c r="A1702" s="1" t="n">
-        <v>46079.6910300926</v>
+        <v>46079.3333333333</v>
       </c>
       <c r="B1702" t="n">
         <v>46000</v>
@@ -46043,6 +46043,32 @@
         <v>148</v>
       </c>
       <c r="H1702" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="1" t="n">
+        <v>46080.6917592593</v>
+      </c>
+      <c r="B1703" t="n">
+        <v>64000</v>
+      </c>
+      <c r="C1703" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="D1703" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1703" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="F1703" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1703" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1703" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46048,7 +46048,7 @@
     </row>
     <row r="1703">
       <c r="A1703" s="1" t="n">
-        <v>46080.6917592593</v>
+        <v>46080.3333333333</v>
       </c>
       <c r="B1703" t="n">
         <v>64000</v>
@@ -46069,6 +46069,32 @@
         <v>204</v>
       </c>
       <c r="H1703" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="1" t="n">
+        <v>46083.6911574074</v>
+      </c>
+      <c r="B1704" t="n">
+        <v>183000</v>
+      </c>
+      <c r="C1704" t="n">
+        <v>3.34999990463257</v>
+      </c>
+      <c r="D1704" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="E1704" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="F1704" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="G1704" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1704" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="483">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1458,6 +1458,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.67000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30999994277954</t>
   </si>
 </sst>
 </file>
@@ -46074,7 +46077,7 @@
     </row>
     <row r="1704">
       <c r="A1704" s="1" t="n">
-        <v>46083.6911574074</v>
+        <v>46083.3333333333</v>
       </c>
       <c r="B1704" t="n">
         <v>183000</v>
@@ -46095,6 +46098,32 @@
         <v>168</v>
       </c>
       <c r="H1704" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="1" t="n">
+        <v>46084.6747569444</v>
+      </c>
+      <c r="B1705" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C1705" t="n">
+        <v>3.30999994277954</v>
+      </c>
+      <c r="D1705" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="E1705" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F1705" t="n">
+        <v>3.30999994277954</v>
+      </c>
+      <c r="G1705" t="s">
+        <v>482</v>
+      </c>
+      <c r="H1705" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46103,7 +46103,7 @@
     </row>
     <row r="1705">
       <c r="A1705" s="1" t="n">
-        <v>46084.6747569444</v>
+        <v>46084.3333333333</v>
       </c>
       <c r="B1705" t="n">
         <v>18000</v>
@@ -46124,6 +46124,32 @@
         <v>482</v>
       </c>
       <c r="H1705" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="1" t="n">
+        <v>46085.5748611111</v>
+      </c>
+      <c r="B1706" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C1706" t="n">
+        <v>3.34999990463257</v>
+      </c>
+      <c r="D1706" t="n">
+        <v>3.28999996185303</v>
+      </c>
+      <c r="E1706" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="F1706" t="n">
+        <v>3.33999991416931</v>
+      </c>
+      <c r="G1706" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1706" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46129,7 +46129,7 @@
     </row>
     <row r="1706">
       <c r="A1706" s="1" t="n">
-        <v>46085.5748611111</v>
+        <v>46085.3333333333</v>
       </c>
       <c r="B1706" t="n">
         <v>21000</v>
@@ -46150,6 +46150,32 @@
         <v>145</v>
       </c>
       <c r="H1706" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="1" t="n">
+        <v>46086.6836226852</v>
+      </c>
+      <c r="B1707" t="n">
+        <v>83000</v>
+      </c>
+      <c r="C1707" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="D1707" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="E1707" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="F1707" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="G1707" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1707" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46155,7 +46155,7 @@
     </row>
     <row r="1707">
       <c r="A1707" s="1" t="n">
-        <v>46086.6836226852</v>
+        <v>46086.3333333333</v>
       </c>
       <c r="B1707" t="n">
         <v>83000</v>
@@ -46176,6 +46176,32 @@
         <v>168</v>
       </c>
       <c r="H1707" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="1" t="n">
+        <v>46087.665462963</v>
+      </c>
+      <c r="B1708" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1708" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D1708" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E1708" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F1708" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G1708" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1708" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46181,7 +46181,7 @@
     </row>
     <row r="1708">
       <c r="A1708" s="1" t="n">
-        <v>46087.665462963</v>
+        <v>46087.3333333333</v>
       </c>
       <c r="B1708" t="n">
         <v>2000</v>
@@ -46202,6 +46202,32 @@
         <v>206</v>
       </c>
       <c r="H1708" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="1" t="n">
+        <v>46090.5973032407</v>
+      </c>
+      <c r="B1709" t="n">
+        <v>42000</v>
+      </c>
+      <c r="C1709" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="D1709" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="E1709" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="F1709" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1709" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1709" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46207,7 +46207,7 @@
     </row>
     <row r="1709">
       <c r="A1709" s="1" t="n">
-        <v>46090.5973032407</v>
+        <v>46090.3333333333</v>
       </c>
       <c r="B1709" t="n">
         <v>42000</v>
@@ -46228,6 +46228,32 @@
         <v>212</v>
       </c>
       <c r="H1709" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="1" t="n">
+        <v>46091.5621759259</v>
+      </c>
+      <c r="B1710" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1710" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1710" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="E1710" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F1710" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1710" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1710" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46233,7 +46233,7 @@
     </row>
     <row r="1710">
       <c r="A1710" s="1" t="n">
-        <v>46091.5621759259</v>
+        <v>46091.3333333333</v>
       </c>
       <c r="B1710" t="n">
         <v>2000</v>
@@ -46254,6 +46254,32 @@
         <v>212</v>
       </c>
       <c r="H1710" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="1" t="n">
+        <v>46092.6914351852</v>
+      </c>
+      <c r="B1711" t="n">
+        <v>372000</v>
+      </c>
+      <c r="C1711" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1711" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="E1711" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F1711" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="G1711" t="s">
+        <v>148</v>
+      </c>
+      <c r="H1711" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46259,13 +46259,13 @@
     </row>
     <row r="1711">
       <c r="A1711" s="1" t="n">
-        <v>46092.6914351852</v>
+        <v>46092.3333333333</v>
       </c>
       <c r="B1711" t="n">
         <v>372000</v>
       </c>
       <c r="C1711" t="n">
-        <v>3.20000004768372</v>
+        <v>3.21000003814697</v>
       </c>
       <c r="D1711" t="n">
         <v>3.20000004768372</v>
@@ -46280,6 +46280,32 @@
         <v>148</v>
       </c>
       <c r="H1711" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="1" t="n">
+        <v>46093.6910185185</v>
+      </c>
+      <c r="B1712" t="n">
+        <v>254000</v>
+      </c>
+      <c r="C1712" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1712" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1712" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F1712" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1712" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1712" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="484">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1461,6 +1461,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.30999994277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -46285,7 +46288,7 @@
     </row>
     <row r="1712">
       <c r="A1712" s="1" t="n">
-        <v>46093.6910185185</v>
+        <v>46093.3333333333</v>
       </c>
       <c r="B1712" t="n">
         <v>254000</v>
@@ -46306,6 +46309,56 @@
         <v>212</v>
       </c>
       <c r="H1712" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="1" t="n">
+        <v>46094.3333333333</v>
+      </c>
+      <c r="B1713" t="n">
+        <v>110000</v>
+      </c>
+      <c r="C1713" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1713" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1713" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1713"/>
+      <c r="G1713" t="s">
+        <v>483</v>
+      </c>
+      <c r="H1713" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="1" t="n">
+        <v>46094.6912268518</v>
+      </c>
+      <c r="B1714" t="n">
+        <v>110000</v>
+      </c>
+      <c r="C1714" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1714" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1714" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1714" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1714" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1714" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46328,9 +46328,11 @@
       <c r="E1713" t="n">
         <v>3.19000005722046</v>
       </c>
-      <c r="F1713"/>
+      <c r="F1713" t="n">
+        <v>3.20000004768372</v>
+      </c>
       <c r="G1713" t="s">
-        <v>483</v>
+        <v>212</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46338,27 +46340,51 @@
     </row>
     <row r="1714">
       <c r="A1714" s="1" t="n">
-        <v>46094.6912268518</v>
+        <v>46097.3333333333</v>
       </c>
       <c r="B1714" t="n">
-        <v>110000</v>
+        <v>105000</v>
       </c>
       <c r="C1714" t="n">
-        <v>3.20000004768372</v>
+        <v>3.1800000667572</v>
       </c>
       <c r="D1714" t="n">
         <v>3.1800000667572</v>
       </c>
       <c r="E1714" t="n">
-        <v>3.19000005722046</v>
-      </c>
-      <c r="F1714" t="n">
-        <v>3.20000004768372</v>
-      </c>
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1714"/>
       <c r="G1714" t="s">
-        <v>212</v>
+        <v>483</v>
       </c>
       <c r="H1714" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="1" t="n">
+        <v>46097.5224305556</v>
+      </c>
+      <c r="B1715" t="n">
+        <v>105000</v>
+      </c>
+      <c r="C1715" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="D1715" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1715" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1715" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1715" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1715" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46354,9 +46354,11 @@
       <c r="E1714" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="F1714"/>
+      <c r="F1714" t="n">
+        <v>3.1800000667572</v>
+      </c>
       <c r="G1714" t="s">
-        <v>483</v>
+        <v>166</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46364,10 +46366,10 @@
     </row>
     <row r="1715">
       <c r="A1715" s="1" t="n">
-        <v>46097.5224305556</v>
+        <v>46098.3333333333</v>
       </c>
       <c r="B1715" t="n">
-        <v>105000</v>
+        <v>10000</v>
       </c>
       <c r="C1715" t="n">
         <v>3.1800000667572</v>
@@ -46378,13 +46380,37 @@
       <c r="E1715" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="F1715" t="n">
+      <c r="F1715"/>
+      <c r="G1715" t="s">
+        <v>483</v>
+      </c>
+      <c r="H1715" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="1" t="n">
+        <v>46098.63375</v>
+      </c>
+      <c r="B1716" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C1716" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="G1715" t="s">
+      <c r="D1716" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1716" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1716" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1716" t="s">
         <v>166</v>
       </c>
-      <c r="H1715" t="s">
+      <c r="H1716" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46380,9 +46380,11 @@
       <c r="E1715" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="F1715"/>
+      <c r="F1715" t="n">
+        <v>3.1800000667572</v>
+      </c>
       <c r="G1715" t="s">
-        <v>483</v>
+        <v>166</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46390,10 +46392,10 @@
     </row>
     <row r="1716">
       <c r="A1716" s="1" t="n">
-        <v>46098.63375</v>
+        <v>46099.3333333333</v>
       </c>
       <c r="B1716" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="C1716" t="n">
         <v>3.1800000667572</v>
@@ -46404,13 +46406,37 @@
       <c r="E1716" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="F1716" t="n">
+      <c r="F1716"/>
+      <c r="G1716" t="s">
+        <v>483</v>
+      </c>
+      <c r="H1716" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="1" t="n">
+        <v>46099.4492708333</v>
+      </c>
+      <c r="B1717" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1717" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="G1716" t="s">
+      <c r="D1717" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1717" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1717" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1717" t="s">
         <v>166</v>
       </c>
-      <c r="H1716" t="s">
+      <c r="H1717" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46406,9 +46406,11 @@
       <c r="E1716" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="F1716"/>
+      <c r="F1716" t="n">
+        <v>3.1800000667572</v>
+      </c>
       <c r="G1716" t="s">
-        <v>483</v>
+        <v>166</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46416,10 +46418,10 @@
     </row>
     <row r="1717">
       <c r="A1717" s="1" t="n">
-        <v>46099.4492708333</v>
+        <v>46100.3333333333</v>
       </c>
       <c r="B1717" t="n">
-        <v>1000</v>
+        <v>12000</v>
       </c>
       <c r="C1717" t="n">
         <v>3.1800000667572</v>
@@ -46430,13 +46432,37 @@
       <c r="E1717" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="F1717" t="n">
+      <c r="F1717"/>
+      <c r="G1717" t="s">
+        <v>483</v>
+      </c>
+      <c r="H1717" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="1" t="n">
+        <v>46100.65875</v>
+      </c>
+      <c r="B1718" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C1718" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="G1717" t="s">
+      <c r="D1718" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1718" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1718" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1718" t="s">
         <v>166</v>
       </c>
-      <c r="H1717" t="s">
+      <c r="H1718" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46432,9 +46432,11 @@
       <c r="E1717" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="F1717"/>
+      <c r="F1717" t="n">
+        <v>3.1800000667572</v>
+      </c>
       <c r="G1717" t="s">
-        <v>483</v>
+        <v>166</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46442,10 +46444,10 @@
     </row>
     <row r="1718">
       <c r="A1718" s="1" t="n">
-        <v>46100.65875</v>
+        <v>46101.3333333333</v>
       </c>
       <c r="B1718" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="C1718" t="n">
         <v>3.1800000667572</v>
@@ -46456,13 +46458,37 @@
       <c r="E1718" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="F1718" t="n">
+      <c r="F1718"/>
+      <c r="G1718" t="s">
+        <v>483</v>
+      </c>
+      <c r="H1718" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="1" t="n">
+        <v>46101.4340393519</v>
+      </c>
+      <c r="B1719" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1719" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="G1718" t="s">
+      <c r="D1719" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1719" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1719" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1719" t="s">
         <v>166</v>
       </c>
-      <c r="H1718" t="s">
+      <c r="H1719" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46458,9 +46458,11 @@
       <c r="E1718" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="F1718"/>
+      <c r="F1718" t="n">
+        <v>3.1800000667572</v>
+      </c>
       <c r="G1718" t="s">
-        <v>483</v>
+        <v>166</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46468,13 +46470,13 @@
     </row>
     <row r="1719">
       <c r="A1719" s="1" t="n">
-        <v>46101.4340393519</v>
+        <v>46104.3333333333</v>
       </c>
       <c r="B1719" t="n">
-        <v>6000</v>
+        <v>166000</v>
       </c>
       <c r="C1719" t="n">
-        <v>3.1800000667572</v>
+        <v>3.20000004768372</v>
       </c>
       <c r="D1719" t="n">
         <v>3.1800000667572</v>
@@ -46482,13 +46484,37 @@
       <c r="E1719" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="F1719" t="n">
+      <c r="F1719"/>
+      <c r="G1719" t="s">
+        <v>483</v>
+      </c>
+      <c r="H1719" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="1" t="n">
+        <v>46104.6023958333</v>
+      </c>
+      <c r="B1720" t="n">
+        <v>166000</v>
+      </c>
+      <c r="C1720" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1720" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="G1719" t="s">
-        <v>166</v>
-      </c>
-      <c r="H1719" t="s">
+      <c r="E1720" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1720" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1720" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1720" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46484,9 +46484,11 @@
       <c r="E1719" t="n">
         <v>3.1800000667572</v>
       </c>
-      <c r="F1719"/>
+      <c r="F1719" t="n">
+        <v>3.20000004768372</v>
+      </c>
       <c r="G1719" t="s">
-        <v>483</v>
+        <v>212</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46494,27 +46496,51 @@
     </row>
     <row r="1720">
       <c r="A1720" s="1" t="n">
-        <v>46104.6023958333</v>
+        <v>46105.3333333333</v>
       </c>
       <c r="B1720" t="n">
-        <v>166000</v>
+        <v>9000</v>
       </c>
       <c r="C1720" t="n">
-        <v>3.20000004768372</v>
+        <v>3.19000005722046</v>
       </c>
       <c r="D1720" t="n">
-        <v>3.1800000667572</v>
+        <v>3.19000005722046</v>
       </c>
       <c r="E1720" t="n">
-        <v>3.1800000667572</v>
-      </c>
-      <c r="F1720" t="n">
-        <v>3.20000004768372</v>
-      </c>
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1720"/>
       <c r="G1720" t="s">
-        <v>212</v>
+        <v>483</v>
       </c>
       <c r="H1720" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="1" t="n">
+        <v>46105.6255671296</v>
+      </c>
+      <c r="B1721" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1721" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1721" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1721" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1721" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1721" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1721" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46510,9 +46510,11 @@
       <c r="E1720" t="n">
         <v>3.19000005722046</v>
       </c>
-      <c r="F1720"/>
+      <c r="F1720" t="n">
+        <v>3.19000005722046</v>
+      </c>
       <c r="G1720" t="s">
-        <v>483</v>
+        <v>204</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46520,27 +46522,51 @@
     </row>
     <row r="1721">
       <c r="A1721" s="1" t="n">
-        <v>46105.6255671296</v>
+        <v>46106.3333333333</v>
       </c>
       <c r="B1721" t="n">
-        <v>9000</v>
+        <v>29000</v>
       </c>
       <c r="C1721" t="n">
-        <v>3.19000005722046</v>
+        <v>3.20000004768372</v>
       </c>
       <c r="D1721" t="n">
-        <v>3.19000005722046</v>
+        <v>3.1800000667572</v>
       </c>
       <c r="E1721" t="n">
         <v>3.19000005722046</v>
       </c>
-      <c r="F1721" t="n">
+      <c r="F1721"/>
+      <c r="G1721" t="s">
+        <v>483</v>
+      </c>
+      <c r="H1721" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="1" t="n">
+        <v>46106.6714930556</v>
+      </c>
+      <c r="B1722" t="n">
+        <v>29000</v>
+      </c>
+      <c r="C1722" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1722" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1722" t="n">
         <v>3.19000005722046</v>
       </c>
-      <c r="G1721" t="s">
-        <v>204</v>
-      </c>
-      <c r="H1721" t="s">
+      <c r="F1722" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G1722" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1722" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46536,9 +46536,11 @@
       <c r="E1721" t="n">
         <v>3.19000005722046</v>
       </c>
-      <c r="F1721"/>
+      <c r="F1721" t="n">
+        <v>3.1800000667572</v>
+      </c>
       <c r="G1721" t="s">
-        <v>483</v>
+        <v>166</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46546,27 +46548,51 @@
     </row>
     <row r="1722">
       <c r="A1722" s="1" t="n">
-        <v>46106.6714930556</v>
+        <v>46107.3333333333</v>
       </c>
       <c r="B1722" t="n">
-        <v>29000</v>
+        <v>5000</v>
       </c>
       <c r="C1722" t="n">
-        <v>3.20000004768372</v>
+        <v>3.19000005722046</v>
       </c>
       <c r="D1722" t="n">
-        <v>3.1800000667572</v>
+        <v>3.19000005722046</v>
       </c>
       <c r="E1722" t="n">
         <v>3.19000005722046</v>
       </c>
-      <c r="F1722" t="n">
-        <v>3.1800000667572</v>
-      </c>
+      <c r="F1722"/>
       <c r="G1722" t="s">
-        <v>166</v>
+        <v>483</v>
       </c>
       <c r="H1722" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="1" t="n">
+        <v>46107.6699189815</v>
+      </c>
+      <c r="B1723" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C1723" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1723" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1723" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1723" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1723" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1723" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="483">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1461,9 +1461,6 @@
   </si>
   <si>
     <t xml:space="preserve">3.30999994277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -46562,9 +46559,11 @@
       <c r="E1722" t="n">
         <v>3.19000005722046</v>
       </c>
-      <c r="F1722"/>
+      <c r="F1722" t="n">
+        <v>3.19000005722046</v>
+      </c>
       <c r="G1722" t="s">
-        <v>483</v>
+        <v>204</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46572,13 +46571,13 @@
     </row>
     <row r="1723">
       <c r="A1723" s="1" t="n">
-        <v>46107.6699189815</v>
+        <v>46108.3333333333</v>
       </c>
       <c r="B1723" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="C1723" t="n">
-        <v>3.19000005722046</v>
+        <v>3.20000004768372</v>
       </c>
       <c r="D1723" t="n">
         <v>3.19000005722046</v>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46595,6 +46595,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1724">
+      <c r="A1724" s="1" t="n">
+        <v>46111.2916666667</v>
+      </c>
+      <c r="B1724" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C1724" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1724" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1724" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1724" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1724" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1724" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46621,6 +46621,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1725">
+      <c r="A1725" s="1" t="n">
+        <v>46112.2916666667</v>
+      </c>
+      <c r="B1725" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1725" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1725" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1725" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1725" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1725" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1725" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46647,6 +46647,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1726">
+      <c r="A1726" s="1" t="n">
+        <v>46113.2916666667</v>
+      </c>
+      <c r="B1726" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C1726" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1726" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1726" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1726" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1726" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1726" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46673,6 +46673,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1727">
+      <c r="A1727" s="1" t="n">
+        <v>46114.2916666667</v>
+      </c>
+      <c r="B1727" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1727" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1727" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1727" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1727" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1727" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1727" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46699,6 +46699,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1728">
+      <c r="A1728" s="1" t="n">
+        <v>46119.5340972222</v>
+      </c>
+      <c r="B1728" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C1728" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1728" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1728" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F1728" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1728" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1728" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46701,7 +46701,7 @@
     </row>
     <row r="1728">
       <c r="A1728" s="1" t="n">
-        <v>46119.5340972222</v>
+        <v>46119.2916666667</v>
       </c>
       <c r="B1728" t="n">
         <v>13000</v>
@@ -46722,6 +46722,32 @@
         <v>204</v>
       </c>
       <c r="H1728" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="1" t="n">
+        <v>46120.2916666667</v>
+      </c>
+      <c r="B1729" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1729" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1729" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1729" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F1729" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1729" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1729" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46751,6 +46751,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1730">
+      <c r="A1730" s="1" t="n">
+        <v>46121.2916666667</v>
+      </c>
+      <c r="B1730" t="n">
+        <v>17000</v>
+      </c>
+      <c r="C1730" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1730" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1730" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1730" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1730" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1730" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46777,6 +46777,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1731">
+      <c r="A1731" s="1" t="n">
+        <v>46122.2916666667</v>
+      </c>
+      <c r="B1731" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C1731" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1731" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1731" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1731" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1731" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1731" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46803,6 +46803,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1732">
+      <c r="A1732" s="1" t="n">
+        <v>46125.2916666667</v>
+      </c>
+      <c r="B1732" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1732" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1732" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1732" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1732" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1732" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1732" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46829,6 +46829,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1733">
+      <c r="A1733" s="1" t="n">
+        <v>46126.2916666667</v>
+      </c>
+      <c r="B1733" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1733" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1733" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1733" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1733" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1733" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1733" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46855,6 +46855,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1734">
+      <c r="A1734" s="1" t="n">
+        <v>46127.2916666667</v>
+      </c>
+      <c r="B1734" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1734" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1734" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="E1734" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F1734" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1734" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1734" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46881,6 +46881,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1735">
+      <c r="A1735" s="1" t="n">
+        <v>46128.2916666667</v>
+      </c>
+      <c r="B1735" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C1735" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1735" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1735" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1735" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1735" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1735" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46907,6 +46907,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1736">
+      <c r="A1736" s="1" t="n">
+        <v>46129.2916666667</v>
+      </c>
+      <c r="B1736" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1736" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1736" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1736" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1736" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1736" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1736" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46933,6 +46933,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1737">
+      <c r="A1737" s="1" t="n">
+        <v>46132.2916666667</v>
+      </c>
+      <c r="B1737" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1737" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1737" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1737" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1737" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1737" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1737" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46959,6 +46959,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1738">
+      <c r="A1738" s="1" t="n">
+        <v>46133.2916666667</v>
+      </c>
+      <c r="B1738" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C1738" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1738" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1738" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1738" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1738" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1738" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELES.MI.xlsx
+++ b/data/ELES.MI.xlsx
@@ -46985,6 +46985,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1739">
+      <c r="A1739" s="1" t="n">
+        <v>46134.2916666667</v>
+      </c>
+      <c r="B1739" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1739" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D1739" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E1739" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F1739" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G1739" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1739" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
